--- a/Mühendis.xlsx
+++ b/Mühendis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F5AC2D-DB51-4D88-9D02-31F846B4C04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F524CFAF-F9C6-4ED1-B0B4-261492AD3930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personel Listesi" sheetId="1" r:id="rId1"/>
@@ -27,70 +27,70 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t>EMİNE ALANLI KIRCILI</t>
-  </si>
-  <si>
-    <t>ESMEN TOKALI</t>
-  </si>
-  <si>
-    <t>HAVVA NİLGÜN KIYMAÇ</t>
-  </si>
-  <si>
-    <t>HİKMET GÜLCAN</t>
-  </si>
-  <si>
-    <t>HİLMİ MÜFTÜOĞLU</t>
-  </si>
-  <si>
-    <t>HÜSEYİN KURT</t>
-  </si>
-  <si>
-    <t>KEMAL KORKMAZ</t>
-  </si>
-  <si>
-    <t>LOKMAN ALKAN</t>
-  </si>
-  <si>
-    <t>MEHMET NEJAT AY</t>
-  </si>
-  <si>
-    <t>SARİYE KUŞÇU</t>
-  </si>
-  <si>
-    <t>SERVET ATA</t>
-  </si>
-  <si>
-    <t>TAHA GÜRKAN</t>
-  </si>
-  <si>
-    <t>CİHAN KARA</t>
-  </si>
-  <si>
-    <t>MEHMET AKGÜN KOLUKIRIK</t>
-  </si>
-  <si>
-    <t>ÖZKAN AKBAŞ</t>
-  </si>
-  <si>
-    <t>TEVFİK YILDIZ</t>
-  </si>
-  <si>
-    <t>BURAK AKBAŞ</t>
-  </si>
-  <si>
-    <t>GÜLİZAR YILDIZ</t>
-  </si>
-  <si>
-    <t>MUHAMMED FURKAN KAPLAN</t>
-  </si>
-  <si>
-    <t>MUSTAFA DIKI</t>
-  </si>
-  <si>
-    <t>MEHTAP AKDOĞAN</t>
-  </si>
-  <si>
-    <t>VOLKAN İZCİ</t>
+    <t>Emine ALANLI KIRCILI</t>
+  </si>
+  <si>
+    <t>Esmen TOKALI</t>
+  </si>
+  <si>
+    <t>Havva NİLGÜN KIYMAÇ</t>
+  </si>
+  <si>
+    <t>Hikmet GÜLCAN</t>
+  </si>
+  <si>
+    <t>Hilmi MÜFTÜOĞLU</t>
+  </si>
+  <si>
+    <t>Hüseyin KURT</t>
+  </si>
+  <si>
+    <t>Kemal KORKMAZ</t>
+  </si>
+  <si>
+    <t>Lokman ALKAN</t>
+  </si>
+  <si>
+    <t>Mehmet NEJAT AY</t>
+  </si>
+  <si>
+    <t>Sariye KUŞÇU</t>
+  </si>
+  <si>
+    <t>Servet ATA</t>
+  </si>
+  <si>
+    <t>Taha GÜRKAN</t>
+  </si>
+  <si>
+    <t>Cihan KARA</t>
+  </si>
+  <si>
+    <t>Mehmet AKGÜN KOLUKIRIK</t>
+  </si>
+  <si>
+    <t>Özkan AKBAŞ</t>
+  </si>
+  <si>
+    <t>Tevfik YILDIZ</t>
+  </si>
+  <si>
+    <t>Burak AKBAŞ</t>
+  </si>
+  <si>
+    <t>Gülizar YILDIZ</t>
+  </si>
+  <si>
+    <t>Muhammed FURKAN KAPLAN</t>
+  </si>
+  <si>
+    <t>Mustafa DIKI</t>
+  </si>
+  <si>
+    <t>Mehtap AKDOĞAN</t>
+  </si>
+  <si>
+    <t>Volkan İZCİ</t>
   </si>
 </sst>
 </file>
@@ -468,125 +468,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.8984375" customWidth="1"/>
+    <col min="1" max="1" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:A15" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/Mühendis.xlsx
+++ b/Mühendis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F524CFAF-F9C6-4ED1-B0B4-261492AD3930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2699D749-131F-425B-B885-88CFA6FB76DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personel Listesi" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Emine ALANLI KIRCILI</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Volkan İZCİ</t>
+  </si>
+  <si>
+    <t>Feyzullah ÇIPLAK</t>
   </si>
 </sst>
 </file>
@@ -467,119 +470,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.875" customWidth="1"/>
+    <col min="1" max="1" width="30.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>21</v>
       </c>
     </row>

--- a/Mühendis.xlsx
+++ b/Mühendis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2699D749-131F-425B-B885-88CFA6FB76DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E5985-86FE-4BF0-9E6D-A7B1DA98198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="4530" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personel Listesi" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Emine ALANLI KIRCILI</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>Feyzullah ÇIPLAK</t>
+  </si>
+  <si>
+    <t>Kenan ZENGİN</t>
   </si>
 </sst>
 </file>
@@ -470,125 +473,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.8984375" customWidth="1"/>
+    <col min="1" max="1" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Mühendis.xlsx
+++ b/Mühendis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E5985-86FE-4BF0-9E6D-A7B1DA98198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8738FCBB-324D-4D48-BC2D-608275FDD7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="4530" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Personel Listesi" sheetId="1" r:id="rId1"/>
@@ -576,27 +576,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Mühendis.xlsx
+++ b/Mühendis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8738FCBB-324D-4D48-BC2D-608275FDD7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE76FAE2-A4A3-44BA-A927-CA23A38757BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Emine ALANLI KIRCILI</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Kenan ZENGİN</t>
+  </si>
+  <si>
+    <t>Fatih ARSLAN</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.875" customWidth="1"/>
@@ -491,111 +494,116 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
